--- a/DEV/org.openl.rules.demo/src/org.openl.rules.demo.examples/Example-4-Reference-Guide/rules/4-Testing/TestTables.xlsx
+++ b/DEV/org.openl.rules.demo/src/org.openl.rules.demo.examples/Example-4-Reference-Guide/rules/4-Testing/TestTables.xlsx
@@ -1650,13 +1650,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:I96"/>
+  <dimension ref="B2:I112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.5" customWidth="1" min="1" max="1"/>
     <col width="70" customWidth="1" min="2" max="2"/>
     <col width="20.9" customWidth="1" min="3" max="3"/>
-    <col width="12.5" customWidth="1" min="4" max="4"/>
+    <col width="39.8" customWidth="1" min="4" max="4"/>
     <col width="14.6" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -1825,7 +1825,7 @@
     <row r="20" ht="30" customHeight="1">
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Precision: "_res_ (2)" compares a number with 2 decimal places, so the difference must be less than 0.01. The "precision" property sets it for the whole test table. A negative precision rounds to tens, hundreds and so on.</t>
+          <t>Precision: "_res_ (2)" compares a number with 2 decimal places, so the difference may be up to 0.01. The "precision" property sets it for the whole test table. A negative precision rounds to tens, hundreds and so on.</t>
         </is>
       </c>
     </row>
@@ -2263,165 +2263,307 @@
       </c>
       <c r="D72" s="6" t="n"/>
     </row>
-    <row r="74" ht="16.5" customHeight="1">
+    <row r="74" ht="30" customHeight="1">
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>A rule that returns Object is checked by the text of the value: "10" matches the number 10.0, the Integer 10 and the text "10".</t>
+          <t>A BigDecimal result is compared with all its digits. Two thirds is 0.6666666666666666666666666666666667 with 34 digits, and a shorter expected value does not match it. A precision allows a difference up to 1E-n, computed exactly: 0.6666666667 matches with "_res_ (10)".</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>Method Object AnyValue(String kind)</t>
+          <t>Method BigDecimal Share(BigDecimal part, BigDecimal whole)</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="B77" s="6" t="inlineStr">
         <is>
+          <t>return part / whole;</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>Test Share ShareTest</t>
+        </is>
+      </c>
+      <c r="C79" s="8" t="n"/>
+      <c r="D79" s="4" t="n"/>
+    </row>
+    <row r="80">
+      <c r="B80" s="9" t="inlineStr">
+        <is>
+          <t>part</t>
+        </is>
+      </c>
+      <c r="C80" s="9" t="inlineStr">
+        <is>
+          <t>whole</t>
+        </is>
+      </c>
+      <c r="D80" s="9" t="inlineStr">
+        <is>
+          <t>_res_</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" s="5" t="inlineStr">
+        <is>
+          <t>Part</t>
+        </is>
+      </c>
+      <c r="C81" s="5" t="inlineStr">
+        <is>
+          <t>Whole</t>
+        </is>
+      </c>
+      <c r="D81" s="5" t="inlineStr">
+        <is>
+          <t>Share</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C82" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D82" s="7" t="inlineStr">
+        <is>
+          <t>0.6666666666666666666666666666666667</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C83" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D83" s="7" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>Test Share SharePrecisionTest</t>
+        </is>
+      </c>
+      <c r="C85" s="8" t="n"/>
+      <c r="D85" s="4" t="n"/>
+    </row>
+    <row r="86">
+      <c r="B86" s="9" t="inlineStr">
+        <is>
+          <t>part</t>
+        </is>
+      </c>
+      <c r="C86" s="9" t="inlineStr">
+        <is>
+          <t>whole</t>
+        </is>
+      </c>
+      <c r="D86" s="9" t="inlineStr">
+        <is>
+          <t>_res_ (10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="B87" s="5" t="inlineStr">
+        <is>
+          <t>Part</t>
+        </is>
+      </c>
+      <c r="C87" s="5" t="inlineStr">
+        <is>
+          <t>Whole</t>
+        </is>
+      </c>
+      <c r="D87" s="5" t="inlineStr">
+        <is>
+          <t>Share</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="B88" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C88" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D88" s="7" t="n">
+        <v>0.6666666667</v>
+      </c>
+    </row>
+    <row r="90" ht="16.5" customHeight="1">
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>A rule that returns Object is checked by the text of the value: "10" matches the number 10.0, the Integer 10 and the text "10".</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>Method Object AnyValue(String kind)</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="B93" s="6" t="inlineStr">
+        <is>
           <t>if (kind == "double") { return 10.0; }</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="B78" s="6" t="inlineStr">
+    <row r="94">
+      <c r="B94" s="6" t="inlineStr">
         <is>
           <t>if (kind == "integer") { return 10; }</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="B79" s="6" t="inlineStr">
+    <row r="95">
+      <c r="B95" s="6" t="inlineStr">
         <is>
           <t>if (kind == "array") { return new double[] {10.0}; }</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="B80" s="6" t="inlineStr">
+    <row r="96">
+      <c r="B96" s="6" t="inlineStr">
         <is>
           <t>return "10";</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="B82" s="3" t="inlineStr">
+    <row r="98">
+      <c r="B98" s="3" t="inlineStr">
         <is>
           <t>Test AnyValue AnyValueTest</t>
         </is>
       </c>
-      <c r="C82" s="4" t="n"/>
-    </row>
-    <row r="83">
-      <c r="B83" s="9" t="inlineStr">
+      <c r="C98" s="4" t="n"/>
+    </row>
+    <row r="99">
+      <c r="B99" s="9" t="inlineStr">
         <is>
           <t>kind</t>
         </is>
       </c>
-      <c r="C83" s="9" t="inlineStr">
+      <c r="C99" s="9" t="inlineStr">
         <is>
           <t>_res_</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="B84" s="5" t="inlineStr">
+    <row r="100">
+      <c r="B100" s="5" t="inlineStr">
         <is>
           <t>Kind</t>
         </is>
       </c>
-      <c r="C84" s="5" t="inlineStr">
+      <c r="C100" s="5" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="B85" s="6" t="inlineStr">
+    <row r="101">
+      <c r="B101" s="6" t="inlineStr">
         <is>
           <t>double</t>
         </is>
       </c>
-      <c r="C85" s="7" t="n">
+      <c r="C101" s="7" t="n">
         <v>10</v>
       </c>
     </row>
-    <row r="86">
-      <c r="B86" s="6" t="inlineStr">
+    <row r="102">
+      <c r="B102" s="6" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="C86" s="7" t="n">
+      <c r="C102" s="7" t="n">
         <v>10</v>
       </c>
     </row>
-    <row r="87">
-      <c r="B87" s="6" t="inlineStr">
+    <row r="103">
+      <c r="B103" s="6" t="inlineStr">
         <is>
           <t>array</t>
         </is>
       </c>
-      <c r="C87" s="7" t="n">
+      <c r="C103" s="7" t="n">
         <v>10</v>
       </c>
     </row>
-    <row r="88">
-      <c r="B88" s="6" t="inlineStr">
+    <row r="104">
+      <c r="B104" s="6" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="C88" s="7" t="n">
+      <c r="C104" s="7" t="n">
         <v>10</v>
       </c>
     </row>
-    <row r="90">
-      <c r="B90" s="3" t="inlineStr">
+    <row r="106">
+      <c r="B106" s="3" t="inlineStr">
         <is>
           <t>Method Object[] AnyArray()</t>
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="B91" s="6" t="inlineStr">
+    <row r="107">
+      <c r="B107" s="6" t="inlineStr">
         <is>
           <t>return new int[] {10, 20};</t>
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="B93" s="3" t="inlineStr">
+    <row r="109">
+      <c r="B109" s="3" t="inlineStr">
         <is>
           <t>Test AnyArray AnyArrayTest</t>
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="B94" s="9" t="inlineStr">
+    <row r="110">
+      <c r="B110" s="9" t="inlineStr">
         <is>
           <t>_res_</t>
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="B95" s="5" t="inlineStr">
+    <row r="111">
+      <c r="B111" s="5" t="inlineStr">
         <is>
           <t>Values</t>
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="B96" s="7" t="inlineStr">
+    <row r="112">
+      <c r="B112" s="7" t="inlineStr">
         <is>
           <t>10, 20</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="14">
-    <mergeCell ref="B74:I74"/>
+  <mergeCells count="17">
+    <mergeCell ref="B90:I90"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B38:C38"/>
     <mergeCell ref="B67:D67"/>
@@ -2431,10 +2573,13 @@
     <mergeCell ref="B20:I20"/>
     <mergeCell ref="B61:C61"/>
     <mergeCell ref="B52:D52"/>
-    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="B98:C98"/>
     <mergeCell ref="B4:I4"/>
     <mergeCell ref="B14:E14"/>
     <mergeCell ref="B43:I43"/>
+    <mergeCell ref="B74:I74"/>
+    <mergeCell ref="B79:D79"/>
+    <mergeCell ref="B85:D85"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>

--- a/DEV/org.openl.rules.demo/src/org.openl.rules.demo.examples/Example-4-Reference-Guide/rules/4-Testing/TestTables.xlsx
+++ b/DEV/org.openl.rules.demo/src/org.openl.rules.demo.examples/Example-4-Reference-Guide/rules/4-Testing/TestTables.xlsx
@@ -886,10 +886,10 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="B13:I13"/>
+    <mergeCell ref="B31:E31"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B31:E31"/>
+    <mergeCell ref="B13:I13"/>
     <mergeCell ref="B29:I29"/>
     <mergeCell ref="B22:I22"/>
     <mergeCell ref="B15:D15"/>
@@ -906,7 +906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:J53"/>
+  <dimension ref="B2:J59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.5" customWidth="1" min="1" max="1"/>
@@ -1623,20 +1623,86 @@
         <v>360</v>
       </c>
     </row>
+    <row r="55" ht="16.5" customHeight="1">
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>In a transposed test table "&gt;table" goes in the column next to the parameter names.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>Test OrderAmount OrderAmountFromDataTransposedTest</t>
+        </is>
+      </c>
+      <c r="C57" s="8" t="n"/>
+      <c r="D57" s="8" t="n"/>
+      <c r="E57" s="8" t="n"/>
+      <c r="F57" s="4" t="n"/>
+    </row>
+    <row r="58">
+      <c r="B58" s="9" t="inlineStr">
+        <is>
+          <t>order</t>
+        </is>
+      </c>
+      <c r="C58" s="9" t="inlineStr">
+        <is>
+          <t>&gt;sampleOrders</t>
+        </is>
+      </c>
+      <c r="D58" s="5" t="inlineStr">
+        <is>
+          <t>Order</t>
+        </is>
+      </c>
+      <c r="E58" s="6" t="inlineStr">
+        <is>
+          <t>small</t>
+        </is>
+      </c>
+      <c r="F58" s="6" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" s="9" t="inlineStr">
+        <is>
+          <t>_res_</t>
+        </is>
+      </c>
+      <c r="C59" s="9" t="n"/>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="E59" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F59" s="7" t="n">
+        <v>360</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="15">
     <mergeCell ref="B11:D11"/>
     <mergeCell ref="B25:J25"/>
     <mergeCell ref="B48:C48"/>
     <mergeCell ref="B42:G42"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="B33:G33"/>
+    <mergeCell ref="B55:I55"/>
     <mergeCell ref="B36:B37"/>
+    <mergeCell ref="B4:I4"/>
     <mergeCell ref="B31:I31"/>
     <mergeCell ref="C36:C37"/>
     <mergeCell ref="B6:D6"/>
     <mergeCell ref="G36:G37"/>
-    <mergeCell ref="B4:I4"/>
+    <mergeCell ref="B57:F57"/>
     <mergeCell ref="B40:I40"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2563,23 +2629,23 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="B90:I90"/>
+    <mergeCell ref="B74:I74"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B38:C38"/>
     <mergeCell ref="B67:D67"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="B31:D31"/>
     <mergeCell ref="B45:D45"/>
+    <mergeCell ref="B79:D79"/>
+    <mergeCell ref="B98:C98"/>
     <mergeCell ref="B20:I20"/>
+    <mergeCell ref="B85:D85"/>
     <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B90:I90"/>
     <mergeCell ref="B52:D52"/>
-    <mergeCell ref="B98:C98"/>
     <mergeCell ref="B4:I4"/>
     <mergeCell ref="B14:E14"/>
     <mergeCell ref="B43:I43"/>
-    <mergeCell ref="B74:I74"/>
-    <mergeCell ref="B79:D79"/>
-    <mergeCell ref="B85:D85"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -3105,7 +3171,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:I10"/>
+  <dimension ref="B2:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.5" customWidth="1" min="1" max="1"/>
@@ -3223,10 +3289,113 @@
         <v>200</v>
       </c>
     </row>
+    <row r="12" ht="16.5" customHeight="1">
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>A Run table can be transposed: the parameter names in the first column and one run per column.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Run OrderAmount OrderAmountTransposedRun</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="n"/>
+      <c r="D14" s="8" t="n"/>
+      <c r="E14" s="4" t="n"/>
+    </row>
+    <row r="15">
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>order.customer.name</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Customer</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>Ann</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>Bob</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>order.customer.member</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Member</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>order.lines[0].product</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>Pen</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>Desk</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>order.lines[0].price</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Price</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>200</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="4">
+    <mergeCell ref="B12:I12"/>
     <mergeCell ref="B6:E6"/>
     <mergeCell ref="B4:I4"/>
+    <mergeCell ref="B14:E14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>

--- a/DEV/org.openl.rules.demo/src/org.openl.rules.demo.examples/Example-4-Reference-Guide/rules/4-Testing/TestTables.xlsx
+++ b/DEV/org.openl.rules.demo/src/org.openl.rules.demo.examples/Example-4-Reference-Guide/rules/4-Testing/TestTables.xlsx
@@ -203,7 +203,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -228,6 +228,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -906,7 +909,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:J59"/>
+  <dimension ref="B2:J60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.5" customWidth="1" min="1" max="1"/>
@@ -1071,184 +1074,177 @@
     <row r="20">
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Method Double OrderAmount(TestOrder order)</t>
-        </is>
-      </c>
+          <t>Spreadsheet Double OrderAmount(TestOrder order)</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="n"/>
     </row>
     <row r="21">
-      <c r="B21" s="6" t="inlineStr">
-        <is>
-          <t>Double amount = sum(order.lines[transform to price * quantity]);</t>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Value</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>if (order.customer.member) { amount = amount * 0.9; }</t>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="C22" s="12" t="inlineStr">
+        <is>
+          <t>= sum(order.lines[transform to price * quantity])</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>return round(amount - 5 * length(order.coupons), 2);</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" s="3" t="inlineStr">
+          <t>Discounted</t>
+        </is>
+      </c>
+      <c r="C23" s="12" t="inlineStr">
+        <is>
+          <t>= order.customer.member ? $Amount * 0.9 : $Amount</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+      <c r="C24" s="12" t="inlineStr">
+        <is>
+          <t>= round($Discounted - 5 * length(order.coupons), 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>Test OrderAmount OrderAmountByFieldsTest</t>
         </is>
       </c>
-      <c r="C25" s="8" t="n"/>
-      <c r="D25" s="8" t="n"/>
-      <c r="E25" s="8" t="n"/>
-      <c r="F25" s="8" t="n"/>
-      <c r="G25" s="8" t="n"/>
-      <c r="H25" s="8" t="n"/>
-      <c r="I25" s="8" t="n"/>
-      <c r="J25" s="4" t="n"/>
-    </row>
-    <row r="26">
-      <c r="B26" s="9" t="inlineStr">
+      <c r="C26" s="8" t="n"/>
+      <c r="D26" s="8" t="n"/>
+      <c r="E26" s="8" t="n"/>
+      <c r="F26" s="8" t="n"/>
+      <c r="G26" s="8" t="n"/>
+      <c r="H26" s="8" t="n"/>
+      <c r="I26" s="8" t="n"/>
+      <c r="J26" s="4" t="n"/>
+    </row>
+    <row r="27">
+      <c r="B27" s="9" t="inlineStr">
         <is>
           <t>order.customer.name</t>
         </is>
       </c>
-      <c r="C26" s="9" t="inlineStr">
+      <c r="C27" s="9" t="inlineStr">
         <is>
           <t>order.customer.member</t>
         </is>
       </c>
-      <c r="D26" s="9" t="inlineStr">
+      <c r="D27" s="9" t="inlineStr">
         <is>
           <t>order.lines[0].product</t>
         </is>
       </c>
-      <c r="E26" s="9" t="inlineStr">
+      <c r="E27" s="9" t="inlineStr">
         <is>
           <t>order.lines[0].price</t>
         </is>
       </c>
-      <c r="F26" s="9" t="inlineStr">
+      <c r="F27" s="9" t="inlineStr">
         <is>
           <t>order.lines[0].quantity</t>
         </is>
       </c>
-      <c r="G26" s="9" t="inlineStr">
+      <c r="G27" s="9" t="inlineStr">
         <is>
           <t>order.lines[1].product</t>
         </is>
       </c>
-      <c r="H26" s="9" t="inlineStr">
+      <c r="H27" s="9" t="inlineStr">
         <is>
           <t>order.lines[1].price</t>
         </is>
       </c>
-      <c r="I26" s="9" t="inlineStr">
+      <c r="I27" s="9" t="inlineStr">
         <is>
           <t>order.coupons</t>
         </is>
       </c>
-      <c r="J26" s="9" t="inlineStr">
+      <c r="J27" s="9" t="inlineStr">
         <is>
           <t>_res_</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="B27" s="5" t="inlineStr">
+    <row r="28">
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>Customer</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
+      <c r="C28" s="5" t="inlineStr">
         <is>
           <t>Member</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="D28" s="5" t="inlineStr">
         <is>
           <t>Product 1</t>
         </is>
       </c>
-      <c r="E27" s="5" t="inlineStr">
+      <c r="E28" s="5" t="inlineStr">
         <is>
           <t>Price 1</t>
         </is>
       </c>
-      <c r="F27" s="5" t="inlineStr">
+      <c r="F28" s="5" t="inlineStr">
         <is>
           <t>Quantity 1</t>
         </is>
       </c>
-      <c r="G27" s="5" t="inlineStr">
+      <c r="G28" s="5" t="inlineStr">
         <is>
           <t>Product 2</t>
         </is>
       </c>
-      <c r="H27" s="5" t="inlineStr">
+      <c r="H28" s="5" t="inlineStr">
         <is>
           <t>Price 2</t>
         </is>
       </c>
-      <c r="I27" s="5" t="inlineStr">
+      <c r="I28" s="5" t="inlineStr">
         <is>
           <t>Coupons</t>
         </is>
       </c>
-      <c r="J27" s="5" t="inlineStr">
+      <c r="J28" s="5" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="B28" s="6" t="inlineStr">
-        <is>
-          <t>Ann</t>
-        </is>
-      </c>
-      <c r="C28" s="6" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="D28" s="6" t="inlineStr">
-        <is>
-          <t>Pen</t>
-        </is>
-      </c>
-      <c r="E28" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F28" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="G28" s="6" t="inlineStr">
-        <is>
-          <t>Book</t>
-        </is>
-      </c>
-      <c r="H28" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="I28" s="6" t="n"/>
-      <c r="J28" s="7" t="n">
-        <v>16</v>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>Bob</t>
+          <t>Ann</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
@@ -1260,450 +1256,486 @@
         <v>2</v>
       </c>
       <c r="F29" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>Book</t>
+        </is>
+      </c>
+      <c r="H29" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="I29" s="6" t="n"/>
+      <c r="J29" s="7" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>Bob</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>Pen</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F30" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="G29" s="6" t="n"/>
-      <c r="H29" s="6" t="n"/>
-      <c r="I29" s="6" t="inlineStr">
+      <c r="G30" s="6" t="n"/>
+      <c r="H30" s="6" t="n"/>
+      <c r="I30" s="6" t="inlineStr">
         <is>
           <t>C1, C2</t>
         </is>
       </c>
-      <c r="J29" s="7" t="n">
+      <c r="J30" s="7" t="n">
         <v>-1</v>
       </c>
     </row>
-    <row r="31" ht="16.5" customHeight="1">
-      <c r="B31" s="2" t="inlineStr">
+    <row r="32" ht="16.5" customHeight="1">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>Matrix structure: an array element per row, the cells of the test case key merged over its rows. A "_PK_" column can serve as the key.</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="B33" s="3" t="inlineStr">
+    <row r="34">
+      <c r="B34" s="3" t="inlineStr">
         <is>
           <t>Test OrderAmount OrderAmountByRowsTest</t>
         </is>
       </c>
-      <c r="C33" s="8" t="n"/>
-      <c r="D33" s="8" t="n"/>
-      <c r="E33" s="8" t="n"/>
-      <c r="F33" s="8" t="n"/>
-      <c r="G33" s="4" t="n"/>
-    </row>
-    <row r="34">
-      <c r="B34" s="9" t="inlineStr">
+      <c r="C34" s="8" t="n"/>
+      <c r="D34" s="8" t="n"/>
+      <c r="E34" s="8" t="n"/>
+      <c r="F34" s="8" t="n"/>
+      <c r="G34" s="4" t="n"/>
+    </row>
+    <row r="35">
+      <c r="B35" s="9" t="inlineStr">
         <is>
           <t>_PK_</t>
         </is>
       </c>
-      <c r="C34" s="9" t="inlineStr">
+      <c r="C35" s="9" t="inlineStr">
         <is>
           <t>order.customer.name</t>
         </is>
       </c>
-      <c r="D34" s="9" t="inlineStr">
+      <c r="D35" s="9" t="inlineStr">
         <is>
           <t>order.lines.product</t>
         </is>
       </c>
-      <c r="E34" s="9" t="inlineStr">
+      <c r="E35" s="9" t="inlineStr">
         <is>
           <t>order.lines.price</t>
         </is>
       </c>
-      <c r="F34" s="9" t="inlineStr">
+      <c r="F35" s="9" t="inlineStr">
         <is>
           <t>order.lines.quantity</t>
         </is>
       </c>
-      <c r="G34" s="9" t="inlineStr">
+      <c r="G35" s="9" t="inlineStr">
         <is>
           <t>_res_</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="B35" s="5" t="inlineStr">
+    <row r="36">
+      <c r="B36" s="5" t="inlineStr">
         <is>
           <t>Case</t>
         </is>
       </c>
-      <c r="C35" s="5" t="inlineStr">
+      <c r="C36" s="5" t="inlineStr">
         <is>
           <t>Customer</t>
         </is>
       </c>
-      <c r="D35" s="5" t="inlineStr">
+      <c r="D36" s="5" t="inlineStr">
         <is>
           <t>Product</t>
         </is>
       </c>
-      <c r="E35" s="5" t="inlineStr">
+      <c r="E36" s="5" t="inlineStr">
         <is>
           <t>Price</t>
         </is>
       </c>
-      <c r="F35" s="5" t="inlineStr">
+      <c r="F36" s="5" t="inlineStr">
         <is>
           <t>Quantity</t>
         </is>
       </c>
-      <c r="G35" s="5" t="inlineStr">
+      <c r="G36" s="5" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="B36" s="6" t="inlineStr">
+    <row r="37">
+      <c r="B37" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C36" s="6" t="inlineStr">
+      <c r="C37" s="6" t="inlineStr">
         <is>
           <t>Ann</t>
         </is>
       </c>
-      <c r="D36" s="6" t="inlineStr">
+      <c r="D37" s="6" t="inlineStr">
         <is>
           <t>Pen</t>
         </is>
       </c>
-      <c r="E36" s="6" t="n">
+      <c r="E37" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="F36" s="6" t="n">
+      <c r="F37" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="G36" s="7" t="n">
+      <c r="G37" s="7" t="n">
         <v>16</v>
       </c>
     </row>
-    <row r="37">
-      <c r="B37" s="10" t="n"/>
-      <c r="C37" s="10" t="n"/>
-      <c r="D37" s="6" t="inlineStr">
+    <row r="38">
+      <c r="B38" s="10" t="n"/>
+      <c r="C38" s="10" t="n"/>
+      <c r="D38" s="6" t="inlineStr">
         <is>
           <t>Book</t>
         </is>
       </c>
-      <c r="E37" s="6" t="n">
+      <c r="E38" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="F37" s="6" t="n">
+      <c r="F38" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="G37" s="10" t="n"/>
-    </row>
-    <row r="38">
-      <c r="B38" s="6" t="inlineStr">
+      <c r="G38" s="10" t="n"/>
+    </row>
+    <row r="39">
+      <c r="B39" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C38" s="6" t="inlineStr">
+      <c r="C39" s="6" t="inlineStr">
         <is>
           <t>Bob</t>
         </is>
       </c>
-      <c r="D38" s="6" t="inlineStr">
+      <c r="D39" s="6" t="inlineStr">
         <is>
           <t>Cup</t>
         </is>
       </c>
-      <c r="E38" s="6" t="n">
+      <c r="E39" s="6" t="n">
         <v>4.5</v>
       </c>
-      <c r="F38" s="6" t="n">
+      <c r="F39" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="G38" s="7" t="n">
+      <c r="G39" s="7" t="n">
         <v>9</v>
       </c>
     </row>
-    <row r="40" ht="16.5" customHeight="1">
-      <c r="B40" s="2" t="inlineStr">
+    <row r="41" ht="16.5" customHeight="1">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>"&gt;table" under a parameter name takes whole objects from a data table: the cell value is the key of the row.</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="B42" s="3" t="inlineStr">
+    <row r="43">
+      <c r="B43" s="3" t="inlineStr">
         <is>
           <t>Data TestOrder sampleOrders</t>
         </is>
       </c>
-      <c r="C42" s="8" t="n"/>
-      <c r="D42" s="8" t="n"/>
-      <c r="E42" s="8" t="n"/>
-      <c r="F42" s="8" t="n"/>
-      <c r="G42" s="4" t="n"/>
-    </row>
-    <row r="43">
-      <c r="B43" s="9" t="inlineStr">
+      <c r="C43" s="8" t="n"/>
+      <c r="D43" s="8" t="n"/>
+      <c r="E43" s="8" t="n"/>
+      <c r="F43" s="8" t="n"/>
+      <c r="G43" s="4" t="n"/>
+    </row>
+    <row r="44">
+      <c r="B44" s="9" t="inlineStr">
         <is>
           <t>_PK_</t>
         </is>
       </c>
-      <c r="C43" s="9" t="inlineStr">
+      <c r="C44" s="9" t="inlineStr">
         <is>
           <t>customer.name</t>
         </is>
       </c>
-      <c r="D43" s="9" t="inlineStr">
+      <c r="D44" s="9" t="inlineStr">
         <is>
           <t>customer.member</t>
         </is>
       </c>
-      <c r="E43" s="9" t="inlineStr">
+      <c r="E44" s="9" t="inlineStr">
         <is>
           <t>lines[0].product</t>
         </is>
       </c>
-      <c r="F43" s="9" t="inlineStr">
+      <c r="F44" s="9" t="inlineStr">
         <is>
           <t>lines[0].price</t>
         </is>
       </c>
-      <c r="G43" s="9" t="inlineStr">
+      <c r="G44" s="9" t="inlineStr">
         <is>
           <t>lines[0].quantity</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="B44" s="5" t="inlineStr">
+    <row r="45">
+      <c r="B45" s="5" t="inlineStr">
         <is>
           <t>Order</t>
         </is>
       </c>
-      <c r="C44" s="5" t="inlineStr">
+      <c r="C45" s="5" t="inlineStr">
         <is>
           <t>Customer</t>
         </is>
       </c>
-      <c r="D44" s="5" t="inlineStr">
+      <c r="D45" s="5" t="inlineStr">
         <is>
           <t>Member</t>
         </is>
       </c>
-      <c r="E44" s="5" t="inlineStr">
+      <c r="E45" s="5" t="inlineStr">
         <is>
           <t>Product</t>
         </is>
       </c>
-      <c r="F44" s="5" t="inlineStr">
+      <c r="F45" s="5" t="inlineStr">
         <is>
           <t>Price</t>
         </is>
       </c>
-      <c r="G44" s="5" t="inlineStr">
+      <c r="G45" s="5" t="inlineStr">
         <is>
           <t>Quantity</t>
         </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" s="6" t="inlineStr">
-        <is>
-          <t>small</t>
-        </is>
-      </c>
-      <c r="C45" s="6" t="inlineStr">
-        <is>
-          <t>Carl</t>
-        </is>
-      </c>
-      <c r="D45" s="6" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E45" s="6" t="inlineStr">
-        <is>
-          <t>Pen</t>
-        </is>
-      </c>
-      <c r="F45" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="G45" s="6" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="46">
       <c r="B46" s="6" t="inlineStr">
         <is>
+          <t>small</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>Carl</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E46" s="6" t="inlineStr">
+        <is>
+          <t>Pen</t>
+        </is>
+      </c>
+      <c r="F46" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G46" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="6" t="inlineStr">
+        <is>
           <t>large</t>
         </is>
       </c>
-      <c r="C46" s="6" t="inlineStr">
+      <c r="C47" s="6" t="inlineStr">
         <is>
           <t>Dina</t>
         </is>
       </c>
-      <c r="D46" s="6" t="inlineStr">
+      <c r="D47" s="6" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="E46" s="6" t="inlineStr">
+      <c r="E47" s="6" t="inlineStr">
         <is>
           <t>Desk</t>
         </is>
       </c>
-      <c r="F46" s="6" t="n">
+      <c r="F47" s="6" t="n">
         <v>200</v>
       </c>
-      <c r="G46" s="6" t="n">
+      <c r="G47" s="6" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="48">
-      <c r="B48" s="3" t="inlineStr">
+    <row r="49">
+      <c r="B49" s="3" t="inlineStr">
         <is>
           <t>Test OrderAmount OrderAmountFromDataTest</t>
         </is>
       </c>
-      <c r="C48" s="4" t="n"/>
-    </row>
-    <row r="49">
-      <c r="B49" s="9" t="inlineStr">
-        <is>
-          <t>order</t>
-        </is>
-      </c>
-      <c r="C49" s="9" t="inlineStr">
-        <is>
-          <t>_res_</t>
-        </is>
-      </c>
+      <c r="C49" s="4" t="n"/>
     </row>
     <row r="50">
       <c r="B50" s="9" t="inlineStr">
         <is>
+          <t>order</t>
+        </is>
+      </c>
+      <c r="C50" s="9" t="inlineStr">
+        <is>
+          <t>_res_</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="9" t="inlineStr">
+        <is>
           <t>&gt;sampleOrders</t>
         </is>
       </c>
-      <c r="C50" s="9" t="n"/>
-    </row>
-    <row r="51">
-      <c r="B51" s="5" t="inlineStr">
+      <c r="C51" s="9" t="n"/>
+    </row>
+    <row r="52">
+      <c r="B52" s="5" t="inlineStr">
         <is>
           <t>Order</t>
         </is>
       </c>
-      <c r="C51" s="5" t="inlineStr">
+      <c r="C52" s="5" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="B52" s="6" t="inlineStr">
-        <is>
-          <t>small</t>
-        </is>
-      </c>
-      <c r="C52" s="7" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="53">
       <c r="B53" s="6" t="inlineStr">
         <is>
+          <t>small</t>
+        </is>
+      </c>
+      <c r="C53" s="7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="6" t="inlineStr">
+        <is>
           <t>large</t>
         </is>
       </c>
-      <c r="C53" s="7" t="n">
+      <c r="C54" s="7" t="n">
         <v>360</v>
       </c>
     </row>
-    <row r="55" ht="16.5" customHeight="1">
-      <c r="B55" s="2" t="inlineStr">
+    <row r="56" ht="16.5" customHeight="1">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>In a transposed test table "&gt;table" goes in the column next to the parameter names.</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="B57" s="3" t="inlineStr">
+    <row r="58">
+      <c r="B58" s="3" t="inlineStr">
         <is>
           <t>Test OrderAmount OrderAmountFromDataTransposedTest</t>
         </is>
       </c>
-      <c r="C57" s="8" t="n"/>
-      <c r="D57" s="8" t="n"/>
-      <c r="E57" s="8" t="n"/>
-      <c r="F57" s="4" t="n"/>
-    </row>
-    <row r="58">
-      <c r="B58" s="9" t="inlineStr">
-        <is>
-          <t>order</t>
-        </is>
-      </c>
-      <c r="C58" s="9" t="inlineStr">
-        <is>
-          <t>&gt;sampleOrders</t>
-        </is>
-      </c>
-      <c r="D58" s="5" t="inlineStr">
-        <is>
-          <t>Order</t>
-        </is>
-      </c>
-      <c r="E58" s="6" t="inlineStr">
-        <is>
-          <t>small</t>
-        </is>
-      </c>
-      <c r="F58" s="6" t="inlineStr">
-        <is>
-          <t>large</t>
-        </is>
-      </c>
+      <c r="C58" s="8" t="n"/>
+      <c r="D58" s="8" t="n"/>
+      <c r="E58" s="8" t="n"/>
+      <c r="F58" s="4" t="n"/>
     </row>
     <row r="59">
       <c r="B59" s="9" t="inlineStr">
         <is>
+          <t>order</t>
+        </is>
+      </c>
+      <c r="C59" s="9" t="inlineStr">
+        <is>
+          <t>&gt;sampleOrders</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>Order</t>
+        </is>
+      </c>
+      <c r="E59" s="6" t="inlineStr">
+        <is>
+          <t>small</t>
+        </is>
+      </c>
+      <c r="F59" s="6" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="9" t="inlineStr">
+        <is>
           <t>_res_</t>
         </is>
       </c>
-      <c r="C59" s="9" t="n"/>
-      <c r="D59" s="5" t="inlineStr">
+      <c r="C60" s="9" t="n"/>
+      <c r="D60" s="5" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="E59" s="7" t="n">
+      <c r="E60" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F59" s="7" t="n">
+      <c r="F60" s="7" t="n">
         <v>360</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="16">
     <mergeCell ref="B11:D11"/>
-    <mergeCell ref="B25:J25"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B42:G42"/>
+    <mergeCell ref="B26:J26"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="B56:I56"/>
+    <mergeCell ref="B34:G34"/>
     <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B33:G33"/>
-    <mergeCell ref="B55:I55"/>
-    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B37:B38"/>
+    <mergeCell ref="C37:C38"/>
+    <mergeCell ref="G37:G38"/>
+    <mergeCell ref="B43:G43"/>
+    <mergeCell ref="B41:I41"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B32:I32"/>
     <mergeCell ref="B4:I4"/>
-    <mergeCell ref="B31:I31"/>
-    <mergeCell ref="C36:C37"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="G36:G37"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B40:I40"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -1716,7 +1748,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:I112"/>
+  <dimension ref="B2:I115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.5" customWidth="1" min="1" max="1"/>
@@ -1787,788 +1819,837 @@
     <row r="11">
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Method TestRange RangeOf(Integer[] numbers)</t>
-        </is>
-      </c>
+          <t>Spreadsheet TestRange RangeOf(Integer[] numbers)</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="n"/>
     </row>
     <row r="12">
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>return new TestRange(low = min(numbers), high = max(numbers), values = sort(numbers));</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>= new TestRange(low = min(numbers), high = max(numbers), values = sort(numbers))</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>Test RangeOf RangeOfTest</t>
         </is>
       </c>
-      <c r="C14" s="8" t="n"/>
-      <c r="D14" s="8" t="n"/>
-      <c r="E14" s="4" t="n"/>
-    </row>
-    <row r="15">
-      <c r="B15" s="9" t="inlineStr">
+      <c r="C15" s="8" t="n"/>
+      <c r="D15" s="8" t="n"/>
+      <c r="E15" s="4" t="n"/>
+    </row>
+    <row r="16">
+      <c r="B16" s="9" t="inlineStr">
         <is>
           <t>numbers</t>
         </is>
       </c>
-      <c r="C15" s="9" t="inlineStr">
+      <c r="C16" s="9" t="inlineStr">
         <is>
           <t>_res_.low</t>
         </is>
       </c>
-      <c r="D15" s="9" t="inlineStr">
+      <c r="D16" s="9" t="inlineStr">
         <is>
           <t>_res_.high</t>
         </is>
       </c>
-      <c r="E15" s="9" t="inlineStr">
+      <c r="E16" s="9" t="inlineStr">
         <is>
           <t>_res_.values</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="B16" s="5" t="inlineStr">
+    <row r="17">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>Numbers</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>Sorted</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>5, 3, 9</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="D17" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="E17" s="7" t="inlineStr">
-        <is>
-          <t>3, 5, 9</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="6" t="inlineStr">
         <is>
+          <t>5, 3, 9</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D18" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>3, 5, 9</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="6" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="C18" s="7" t="n">
+      <c r="C19" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="D18" s="7" t="n">
+      <c r="D19" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="E18" s="7" t="inlineStr">
+      <c r="E19" s="7" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="30" customHeight="1">
-      <c r="B20" s="2" t="inlineStr">
+    <row r="21" ht="30" customHeight="1">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>Precision: "_res_ (2)" compares a number with 2 decimal places, so the difference may be up to 0.01. The "precision" property sets it for the whole test table. A negative precision rounds to tens, hundreds and so on.</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Method Double Circle(Double radius)</t>
-        </is>
-      </c>
-    </row>
     <row r="23">
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>return PI * radius * radius;</t>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Spreadsheet Double Circle(Double radius)</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="n"/>
+    </row>
+    <row r="24">
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Value</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="inlineStr">
+        <is>
+          <t>= PI * radius * radius</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>Test Circle CircleTest</t>
         </is>
       </c>
-      <c r="C25" s="4" t="n"/>
-    </row>
-    <row r="26">
-      <c r="B26" s="9" t="inlineStr">
+      <c r="C27" s="4" t="n"/>
+    </row>
+    <row r="28">
+      <c r="B28" s="9" t="inlineStr">
         <is>
           <t>radius</t>
         </is>
       </c>
-      <c r="C26" s="9" t="inlineStr">
+      <c r="C28" s="9" t="inlineStr">
         <is>
           <t>_res_ (2)</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="B27" s="5" t="inlineStr">
+    <row r="29">
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>Radius</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
+      <c r="C29" s="5" t="inlineStr">
         <is>
           <t>Area</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="B28" s="6" t="n">
+    <row r="30">
+      <c r="B30" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="C28" s="7" t="n">
+      <c r="C30" s="7" t="n">
         <v>3.14</v>
       </c>
     </row>
-    <row r="29">
-      <c r="B29" s="6" t="n">
+    <row r="31">
+      <c r="B31" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="C29" s="7" t="n">
+      <c r="C31" s="7" t="n">
         <v>12.57</v>
       </c>
     </row>
-    <row r="31">
-      <c r="B31" s="3" t="inlineStr">
+    <row r="33">
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>Test Circle CirclePrecisionTest</t>
         </is>
       </c>
-      <c r="C31" s="8" t="n"/>
-      <c r="D31" s="4" t="n"/>
-    </row>
-    <row r="32">
-      <c r="B32" s="11" t="inlineStr">
+      <c r="C33" s="8" t="n"/>
+      <c r="D33" s="4" t="n"/>
+    </row>
+    <row r="34">
+      <c r="B34" s="11" t="inlineStr">
         <is>
           <t>properties</t>
         </is>
       </c>
-      <c r="C32" s="11" t="inlineStr">
+      <c r="C34" s="11" t="inlineStr">
         <is>
           <t>precision</t>
         </is>
       </c>
-      <c r="D32" s="11" t="n">
+      <c r="D34" s="11" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="33">
-      <c r="B33" s="9" t="inlineStr">
+    <row r="35">
+      <c r="B35" s="9" t="inlineStr">
         <is>
           <t>radius</t>
         </is>
       </c>
-      <c r="C33" s="9" t="inlineStr">
+      <c r="C35" s="9" t="inlineStr">
         <is>
           <t>_res_</t>
         </is>
       </c>
-      <c r="D33" s="9" t="n"/>
-    </row>
-    <row r="34">
-      <c r="B34" s="5" t="inlineStr">
+      <c r="D35" s="9" t="n"/>
+    </row>
+    <row r="36">
+      <c r="B36" s="5" t="inlineStr">
         <is>
           <t>Radius</t>
         </is>
       </c>
-      <c r="C34" s="5" t="inlineStr">
+      <c r="C36" s="5" t="inlineStr">
         <is>
           <t>Area</t>
         </is>
       </c>
-      <c r="D34" s="5" t="n"/>
-    </row>
-    <row r="35">
-      <c r="B35" s="6" t="n">
+      <c r="D36" s="5" t="n"/>
+    </row>
+    <row r="37">
+      <c r="B37" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="C35" s="7" t="n">
+      <c r="C37" s="7" t="n">
         <v>314.16</v>
       </c>
-      <c r="D35" s="6" t="n"/>
-    </row>
-    <row r="36">
-      <c r="B36" s="6" t="n">
+      <c r="D37" s="6" t="n"/>
+    </row>
+    <row r="38">
+      <c r="B38" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="C36" s="7" t="n">
+      <c r="C38" s="7" t="n">
         <v>31415.93</v>
       </c>
-      <c r="D36" s="6" t="n"/>
-    </row>
-    <row r="38">
-      <c r="B38" s="3" t="inlineStr">
+      <c r="D38" s="6" t="n"/>
+    </row>
+    <row r="40">
+      <c r="B40" s="3" t="inlineStr">
         <is>
           <t>Test Circle CircleRoughTest</t>
         </is>
       </c>
-      <c r="C38" s="4" t="n"/>
-    </row>
-    <row r="39">
-      <c r="B39" s="9" t="inlineStr">
+      <c r="C40" s="4" t="n"/>
+    </row>
+    <row r="41">
+      <c r="B41" s="9" t="inlineStr">
         <is>
           <t>radius</t>
         </is>
       </c>
-      <c r="C39" s="9" t="inlineStr">
+      <c r="C41" s="9" t="inlineStr">
         <is>
           <t>_res_ (-2)</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="B40" s="5" t="inlineStr">
+    <row r="42">
+      <c r="B42" s="5" t="inlineStr">
         <is>
           <t>Radius</t>
         </is>
       </c>
-      <c r="C40" s="5" t="inlineStr">
+      <c r="C42" s="5" t="inlineStr">
         <is>
           <t>Area To Hundreds</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="B41" s="6" t="n">
+    <row r="43">
+      <c r="B43" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="C41" s="7" t="n">
+      <c r="C43" s="7" t="n">
         <v>31400</v>
       </c>
     </row>
-    <row r="43" ht="30" customHeight="1">
-      <c r="B43" s="2" t="inlineStr">
+    <row r="45" ht="30" customHeight="1">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>Precision 0 accepts a difference below 1, so 3.14 matches 3. A precision in the column name wins over the "precision" property of the table. A negative precision works for whole numbers too.</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="B45" s="3" t="inlineStr">
+    <row r="47">
+      <c r="B47" s="3" t="inlineStr">
         <is>
           <t>Test Circle CircleWholeTest</t>
         </is>
       </c>
-      <c r="C45" s="8" t="n"/>
-      <c r="D45" s="4" t="n"/>
-    </row>
-    <row r="46">
-      <c r="B46" s="11" t="inlineStr">
+      <c r="C47" s="8" t="n"/>
+      <c r="D47" s="4" t="n"/>
+    </row>
+    <row r="48">
+      <c r="B48" s="11" t="inlineStr">
         <is>
           <t>properties</t>
         </is>
       </c>
-      <c r="C46" s="11" t="inlineStr">
+      <c r="C48" s="11" t="inlineStr">
         <is>
           <t>precision</t>
         </is>
       </c>
-      <c r="D46" s="11" t="n">
+      <c r="D48" s="11" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="47">
-      <c r="B47" s="9" t="inlineStr">
+    <row r="49">
+      <c r="B49" s="9" t="inlineStr">
         <is>
           <t>radius</t>
         </is>
       </c>
-      <c r="C47" s="9" t="inlineStr">
+      <c r="C49" s="9" t="inlineStr">
         <is>
           <t>_res_</t>
         </is>
       </c>
-      <c r="D47" s="9" t="n"/>
-    </row>
-    <row r="48">
-      <c r="B48" s="5" t="inlineStr">
+      <c r="D49" s="9" t="n"/>
+    </row>
+    <row r="50">
+      <c r="B50" s="5" t="inlineStr">
         <is>
           <t>Radius</t>
         </is>
       </c>
-      <c r="C48" s="5" t="inlineStr">
+      <c r="C50" s="5" t="inlineStr">
         <is>
           <t>Area</t>
         </is>
       </c>
-      <c r="D48" s="5" t="n"/>
-    </row>
-    <row r="49">
-      <c r="B49" s="6" t="n">
+      <c r="D50" s="5" t="n"/>
+    </row>
+    <row r="51">
+      <c r="B51" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="C49" s="7" t="n">
+      <c r="C51" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="D49" s="6" t="n"/>
-    </row>
-    <row r="50">
-      <c r="B50" s="6" t="n">
+      <c r="D51" s="6" t="n"/>
+    </row>
+    <row r="52">
+      <c r="B52" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="C50" s="7" t="n">
+      <c r="C52" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="D50" s="6" t="n"/>
-    </row>
-    <row r="52">
-      <c r="B52" s="3" t="inlineStr">
+      <c r="D52" s="6" t="n"/>
+    </row>
+    <row r="54">
+      <c r="B54" s="3" t="inlineStr">
         <is>
           <t>Test Circle CircleColumnPrecisionTest</t>
         </is>
       </c>
-      <c r="C52" s="8" t="n"/>
-      <c r="D52" s="4" t="n"/>
-    </row>
-    <row r="53">
-      <c r="B53" s="11" t="inlineStr">
+      <c r="C54" s="8" t="n"/>
+      <c r="D54" s="4" t="n"/>
+    </row>
+    <row r="55">
+      <c r="B55" s="11" t="inlineStr">
         <is>
           <t>properties</t>
         </is>
       </c>
-      <c r="C53" s="11" t="inlineStr">
+      <c r="C55" s="11" t="inlineStr">
         <is>
           <t>precision</t>
         </is>
       </c>
-      <c r="D53" s="11" t="n">
+      <c r="D55" s="11" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="54">
-      <c r="B54" s="9" t="inlineStr">
+    <row r="56">
+      <c r="B56" s="9" t="inlineStr">
         <is>
           <t>radius</t>
         </is>
       </c>
-      <c r="C54" s="9" t="inlineStr">
+      <c r="C56" s="9" t="inlineStr">
         <is>
           <t>_res_ (3)</t>
         </is>
       </c>
-      <c r="D54" s="9" t="n"/>
-    </row>
-    <row r="55">
-      <c r="B55" s="5" t="inlineStr">
+      <c r="D56" s="9" t="n"/>
+    </row>
+    <row r="57">
+      <c r="B57" s="5" t="inlineStr">
         <is>
           <t>Radius</t>
         </is>
       </c>
-      <c r="C55" s="5" t="inlineStr">
+      <c r="C57" s="5" t="inlineStr">
         <is>
           <t>Area</t>
         </is>
       </c>
-      <c r="D55" s="5" t="n"/>
-    </row>
-    <row r="56">
-      <c r="B56" s="6" t="n">
+      <c r="D57" s="5" t="n"/>
+    </row>
+    <row r="58">
+      <c r="B58" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="C56" s="7" t="n">
+      <c r="C58" s="7" t="n">
         <v>3.142</v>
       </c>
-      <c r="D56" s="6" t="n"/>
-    </row>
-    <row r="58">
-      <c r="B58" s="3" t="inlineStr">
-        <is>
-          <t>Method Long Population(Integer households)</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="B59" s="6" t="inlineStr">
-        <is>
-          <t>return households * 1234L;</t>
-        </is>
-      </c>
+      <c r="D58" s="6" t="n"/>
+    </row>
+    <row r="60">
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>Spreadsheet Long Population(Integer households)</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="n"/>
     </row>
     <row r="61">
-      <c r="B61" s="3" t="inlineStr">
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+      <c r="C62" s="12" t="inlineStr">
+        <is>
+          <t>= households * 1234L</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" s="3" t="inlineStr">
         <is>
           <t>Test Population PopulationTest</t>
         </is>
       </c>
-      <c r="C61" s="4" t="n"/>
-    </row>
-    <row r="62">
-      <c r="B62" s="9" t="inlineStr">
+      <c r="C64" s="4" t="n"/>
+    </row>
+    <row r="65">
+      <c r="B65" s="9" t="inlineStr">
         <is>
           <t>households</t>
         </is>
       </c>
-      <c r="C62" s="9" t="inlineStr">
+      <c r="C65" s="9" t="inlineStr">
         <is>
           <t>_res_ (-2)</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="B63" s="5" t="inlineStr">
+    <row r="66">
+      <c r="B66" s="5" t="inlineStr">
         <is>
           <t>Households</t>
         </is>
       </c>
-      <c r="C63" s="5" t="inlineStr">
+      <c r="C66" s="5" t="inlineStr">
         <is>
           <t>People To Hundreds</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="B64" s="6" t="n">
+    <row r="67">
+      <c r="B67" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="C64" s="7" t="n">
+      <c r="C67" s="7" t="n">
         <v>12300</v>
       </c>
     </row>
-    <row r="65">
-      <c r="B65" s="6" t="n">
+    <row r="68">
+      <c r="B68" s="6" t="n">
         <v>-10</v>
       </c>
-      <c r="C65" s="7" t="n">
+      <c r="C68" s="7" t="n">
         <v>-12300</v>
       </c>
     </row>
-    <row r="67">
-      <c r="B67" s="3" t="inlineStr">
+    <row r="70">
+      <c r="B70" s="3" t="inlineStr">
         <is>
           <t>Test Population PopulationPropertyTest</t>
         </is>
       </c>
-      <c r="C67" s="8" t="n"/>
-      <c r="D67" s="4" t="n"/>
-    </row>
-    <row r="68">
-      <c r="B68" s="11" t="inlineStr">
+      <c r="C70" s="8" t="n"/>
+      <c r="D70" s="4" t="n"/>
+    </row>
+    <row r="71">
+      <c r="B71" s="11" t="inlineStr">
         <is>
           <t>properties</t>
         </is>
       </c>
-      <c r="C68" s="11" t="inlineStr">
+      <c r="C71" s="11" t="inlineStr">
         <is>
           <t>precision</t>
         </is>
       </c>
-      <c r="D68" s="11" t="n">
+      <c r="D71" s="11" t="n">
         <v>-2</v>
       </c>
     </row>
-    <row r="69">
-      <c r="B69" s="9" t="inlineStr">
+    <row r="72">
+      <c r="B72" s="9" t="inlineStr">
         <is>
           <t>households</t>
         </is>
       </c>
-      <c r="C69" s="9" t="inlineStr">
+      <c r="C72" s="9" t="inlineStr">
         <is>
           <t>_res_</t>
         </is>
       </c>
-      <c r="D69" s="9" t="n"/>
-    </row>
-    <row r="70">
-      <c r="B70" s="5" t="inlineStr">
+      <c r="D72" s="9" t="n"/>
+    </row>
+    <row r="73">
+      <c r="B73" s="5" t="inlineStr">
         <is>
           <t>Households</t>
         </is>
       </c>
-      <c r="C70" s="5" t="inlineStr">
+      <c r="C73" s="5" t="inlineStr">
         <is>
           <t>People To Hundreds</t>
         </is>
       </c>
-      <c r="D70" s="5" t="n"/>
-    </row>
-    <row r="71">
-      <c r="B71" s="6" t="n">
+      <c r="D73" s="5" t="n"/>
+    </row>
+    <row r="74">
+      <c r="B74" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="C71" s="7" t="n">
+      <c r="C74" s="7" t="n">
         <v>123400</v>
       </c>
-      <c r="D71" s="6" t="n"/>
-    </row>
-    <row r="72">
-      <c r="B72" s="6" t="n">
+      <c r="D74" s="6" t="n"/>
+    </row>
+    <row r="75">
+      <c r="B75" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="C72" s="7" t="n">
+      <c r="C75" s="7" t="n">
         <v>3700</v>
       </c>
-      <c r="D72" s="6" t="n"/>
-    </row>
-    <row r="74" ht="30" customHeight="1">
-      <c r="B74" s="2" t="inlineStr">
+      <c r="D75" s="6" t="n"/>
+    </row>
+    <row r="77" ht="30" customHeight="1">
+      <c r="B77" s="2" t="inlineStr">
         <is>
           <t>A BigDecimal result is compared with all its digits. Two thirds is 0.6666666666666666666666666666666667 with 34 digits, and a shorter expected value does not match it. A precision allows a difference up to 1E-n, computed exactly: 0.6666666667 matches with "_res_ (10)".</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="B76" s="3" t="inlineStr">
-        <is>
-          <t>Method BigDecimal Share(BigDecimal part, BigDecimal whole)</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="B77" s="6" t="inlineStr">
-        <is>
-          <t>return part / whole;</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="B79" s="3" t="inlineStr">
         <is>
+          <t>Spreadsheet BigDecimal Share(BigDecimal part, BigDecimal whole)</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="n"/>
+    </row>
+    <row r="80">
+      <c r="B80" s="5" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="C80" s="5" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" s="6" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+      <c r="C81" s="12" t="inlineStr">
+        <is>
+          <t>= part / whole</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" s="3" t="inlineStr">
+        <is>
           <t>Test Share ShareTest</t>
         </is>
       </c>
-      <c r="C79" s="8" t="n"/>
-      <c r="D79" s="4" t="n"/>
-    </row>
-    <row r="80">
-      <c r="B80" s="9" t="inlineStr">
+      <c r="C83" s="8" t="n"/>
+      <c r="D83" s="4" t="n"/>
+    </row>
+    <row r="84">
+      <c r="B84" s="9" t="inlineStr">
         <is>
           <t>part</t>
         </is>
       </c>
-      <c r="C80" s="9" t="inlineStr">
+      <c r="C84" s="9" t="inlineStr">
         <is>
           <t>whole</t>
         </is>
       </c>
-      <c r="D80" s="9" t="inlineStr">
+      <c r="D84" s="9" t="inlineStr">
         <is>
           <t>_res_</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="B81" s="5" t="inlineStr">
+    <row r="85">
+      <c r="B85" s="5" t="inlineStr">
         <is>
           <t>Part</t>
         </is>
       </c>
-      <c r="C81" s="5" t="inlineStr">
+      <c r="C85" s="5" t="inlineStr">
         <is>
           <t>Whole</t>
         </is>
       </c>
-      <c r="D81" s="5" t="inlineStr">
+      <c r="D85" s="5" t="inlineStr">
         <is>
           <t>Share</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="B82" s="6" t="n">
+    <row r="86">
+      <c r="B86" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="C82" s="6" t="n">
+      <c r="C86" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="D82" s="7" t="inlineStr">
+      <c r="D86" s="7" t="inlineStr">
         <is>
           <t>0.6666666666666666666666666666666667</t>
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="B83" s="6" t="n">
+    <row r="87">
+      <c r="B87" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="C83" s="6" t="n">
+      <c r="C87" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="D83" s="7" t="n">
+      <c r="D87" s="7" t="n">
         <v>0.25</v>
       </c>
     </row>
-    <row r="85">
-      <c r="B85" s="3" t="inlineStr">
+    <row r="89">
+      <c r="B89" s="3" t="inlineStr">
         <is>
           <t>Test Share SharePrecisionTest</t>
         </is>
       </c>
-      <c r="C85" s="8" t="n"/>
-      <c r="D85" s="4" t="n"/>
-    </row>
-    <row r="86">
-      <c r="B86" s="9" t="inlineStr">
+      <c r="C89" s="8" t="n"/>
+      <c r="D89" s="4" t="n"/>
+    </row>
+    <row r="90">
+      <c r="B90" s="9" t="inlineStr">
         <is>
           <t>part</t>
         </is>
       </c>
-      <c r="C86" s="9" t="inlineStr">
+      <c r="C90" s="9" t="inlineStr">
         <is>
           <t>whole</t>
         </is>
       </c>
-      <c r="D86" s="9" t="inlineStr">
+      <c r="D90" s="9" t="inlineStr">
         <is>
           <t>_res_ (10)</t>
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="B87" s="5" t="inlineStr">
+    <row r="91">
+      <c r="B91" s="5" t="inlineStr">
         <is>
           <t>Part</t>
         </is>
       </c>
-      <c r="C87" s="5" t="inlineStr">
+      <c r="C91" s="5" t="inlineStr">
         <is>
           <t>Whole</t>
         </is>
       </c>
-      <c r="D87" s="5" t="inlineStr">
+      <c r="D91" s="5" t="inlineStr">
         <is>
           <t>Share</t>
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="B88" s="6" t="n">
+    <row r="92">
+      <c r="B92" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="C88" s="6" t="n">
+      <c r="C92" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="D88" s="7" t="n">
+      <c r="D92" s="7" t="n">
         <v>0.6666666667</v>
       </c>
     </row>
-    <row r="90" ht="16.5" customHeight="1">
-      <c r="B90" s="2" t="inlineStr">
+    <row r="94" ht="16.5" customHeight="1">
+      <c r="B94" s="2" t="inlineStr">
         <is>
           <t>A rule that returns Object is checked by the text of the value: "10" matches the number 10.0, the Integer 10 and the text "10".</t>
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="B92" s="3" t="inlineStr">
-        <is>
-          <t>Method Object AnyValue(String kind)</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="B93" s="6" t="inlineStr">
-        <is>
-          <t>if (kind == "double") { return 10.0; }</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="B94" s="6" t="inlineStr">
-        <is>
-          <t>if (kind == "integer") { return 10; }</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="B95" s="6" t="inlineStr">
-        <is>
-          <t>if (kind == "array") { return new double[] {10.0}; }</t>
-        </is>
-      </c>
-    </row>
     <row r="96">
-      <c r="B96" s="6" t="inlineStr">
-        <is>
-          <t>return "10";</t>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>Spreadsheet Object AnyValue(String kind)</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="n"/>
+    </row>
+    <row r="97">
+      <c r="B97" s="5" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="C97" s="5" t="inlineStr">
+        <is>
+          <t>Value</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="B98" s="3" t="inlineStr">
+      <c r="B98" s="6" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+      <c r="C98" s="12" t="inlineStr">
+        <is>
+          <t>= kind == "double" ? (Object) 10.0 : kind == "integer" ? (Object) 10 : kind == "array" ? (Object) new double[] {10.0} : (Object) "10"</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="B100" s="3" t="inlineStr">
         <is>
           <t>Test AnyValue AnyValueTest</t>
         </is>
       </c>
-      <c r="C98" s="4" t="n"/>
-    </row>
-    <row r="99">
-      <c r="B99" s="9" t="inlineStr">
+      <c r="C100" s="4" t="n"/>
+    </row>
+    <row r="101">
+      <c r="B101" s="9" t="inlineStr">
         <is>
           <t>kind</t>
         </is>
       </c>
-      <c r="C99" s="9" t="inlineStr">
+      <c r="C101" s="9" t="inlineStr">
         <is>
           <t>_res_</t>
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="B100" s="5" t="inlineStr">
+    <row r="102">
+      <c r="B102" s="5" t="inlineStr">
         <is>
           <t>Kind</t>
         </is>
       </c>
-      <c r="C100" s="5" t="inlineStr">
+      <c r="C102" s="5" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="B101" s="6" t="inlineStr">
-        <is>
-          <t>double</t>
-        </is>
-      </c>
-      <c r="C101" s="7" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="B102" s="6" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="C102" s="7" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="103">
       <c r="B103" s="6" t="inlineStr">
         <is>
-          <t>array</t>
+          <t>double</t>
         </is>
       </c>
       <c r="C103" s="7" t="n">
@@ -2578,74 +2659,118 @@
     <row r="104">
       <c r="B104" s="6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="C104" s="7" t="n">
         <v>10</v>
       </c>
     </row>
+    <row r="105">
+      <c r="B105" s="6" t="inlineStr">
+        <is>
+          <t>array</t>
+        </is>
+      </c>
+      <c r="C105" s="7" t="n">
+        <v>10</v>
+      </c>
+    </row>
     <row r="106">
-      <c r="B106" s="3" t="inlineStr">
-        <is>
-          <t>Method Object[] AnyArray()</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="B107" s="6" t="inlineStr">
-        <is>
-          <t>return new int[] {10, 20};</t>
-        </is>
-      </c>
+      <c r="B106" s="6" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="C106" s="7" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="B108" s="3" t="inlineStr">
+        <is>
+          <t>Spreadsheet Object[] AnyArray()</t>
+        </is>
+      </c>
+      <c r="C108" s="4" t="n"/>
     </row>
     <row r="109">
-      <c r="B109" s="3" t="inlineStr">
+      <c r="B109" s="5" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="C109" s="5" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="B110" s="6" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+      <c r="C110" s="12" t="inlineStr">
+        <is>
+          <t>= new int[] {10, 20}</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="B112" s="3" t="inlineStr">
         <is>
           <t>Test AnyArray AnyArrayTest</t>
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="B110" s="9" t="inlineStr">
+    <row r="113">
+      <c r="B113" s="9" t="inlineStr">
         <is>
           <t>_res_</t>
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="B111" s="5" t="inlineStr">
+    <row r="114">
+      <c r="B114" s="5" t="inlineStr">
         <is>
           <t>Values</t>
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="B112" s="7" t="inlineStr">
+    <row r="115">
+      <c r="B115" s="7" t="inlineStr">
         <is>
           <t>10, 20</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="17">
-    <mergeCell ref="B74:I74"/>
+  <mergeCells count="23">
+    <mergeCell ref="B100:C100"/>
+    <mergeCell ref="B15:E15"/>
+    <mergeCell ref="B96:C96"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B21:I21"/>
+    <mergeCell ref="B77:I77"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B83:D83"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B89:D89"/>
+    <mergeCell ref="B4:I4"/>
+    <mergeCell ref="B108:C108"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B47:D47"/>
+    <mergeCell ref="B54:D54"/>
     <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B67:D67"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="B45:D45"/>
-    <mergeCell ref="B79:D79"/>
-    <mergeCell ref="B98:C98"/>
-    <mergeCell ref="B20:I20"/>
-    <mergeCell ref="B85:D85"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B90:I90"/>
-    <mergeCell ref="B52:D52"/>
-    <mergeCell ref="B4:I4"/>
-    <mergeCell ref="B14:E14"/>
-    <mergeCell ref="B43:I43"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B45:I45"/>
+    <mergeCell ref="B94:I94"/>
+    <mergeCell ref="B70:D70"/>
+    <mergeCell ref="B79:C79"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -2658,7 +2783,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:I49"/>
+  <dimension ref="B2:I52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.5" customWidth="1" min="1" max="1"/>
@@ -2686,479 +2811,556 @@
     <row r="6">
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Method Double SafeDivide(Double a, Double b)</t>
-        </is>
-      </c>
+          <t>Spreadsheet Double SafeDivide(Double a, Double b)</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="n"/>
     </row>
     <row r="7">
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>if (b == 0) { error("Division by zero"); }</t>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Value</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>return a / b;</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" s="3" t="inlineStr">
+          <t>Check</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>= if (b == 0) { error("Division by zero"); }</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>= a / b</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>Test SafeDivide SafeDivideTest</t>
         </is>
       </c>
-      <c r="C10" s="8" t="n"/>
-      <c r="D10" s="8" t="n"/>
-      <c r="E10" s="4" t="n"/>
-    </row>
-    <row r="11">
-      <c r="B11" s="9" t="inlineStr">
+      <c r="C11" s="8" t="n"/>
+      <c r="D11" s="8" t="n"/>
+      <c r="E11" s="4" t="n"/>
+    </row>
+    <row r="12">
+      <c r="B12" s="9" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="C12" s="9" t="inlineStr">
         <is>
           <t>b</t>
         </is>
       </c>
-      <c r="D11" s="9" t="inlineStr">
+      <c r="D12" s="9" t="inlineStr">
         <is>
           <t>_res_</t>
         </is>
       </c>
-      <c r="E11" s="9" t="inlineStr">
+      <c r="E12" s="9" t="inlineStr">
         <is>
           <t>_error_</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="B12" s="5" t="inlineStr">
+    <row r="13">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>Error</t>
         </is>
       </c>
-    </row>
-    <row r="13">
-      <c r="B13" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="C13" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="D13" s="7" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="E13" s="7" t="n"/>
     </row>
     <row r="14">
       <c r="B14" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D14" s="7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E14" s="7" t="n"/>
+    </row>
+    <row r="15">
+      <c r="B15" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="C14" s="6" t="n">
+      <c r="C15" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="D14" s="7" t="n"/>
-      <c r="E14" s="7" t="inlineStr">
+      <c r="D15" s="7" t="n"/>
+      <c r="E15" s="7" t="inlineStr">
         <is>
           <t>Division by zero</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Method Integer CheckedAge(Integer age)</t>
-        </is>
-      </c>
-    </row>
     <row r="17">
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>if (age &lt; 0) { error("AGE-01", "Age cannot be negative"); }</t>
-        </is>
-      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Spreadsheet Integer CheckedAge(Integer age)</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="n"/>
     </row>
     <row r="18">
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>if (age &gt; 150) { error("AGE-02", "Age is too high"); }</t>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Value</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>return age;</t>
+          <t>TooLow</t>
+        </is>
+      </c>
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>= if (age &lt; 0) { error("AGE-01", "Age cannot be negative"); }</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>TooHigh</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>= if (age &gt; 150) { error("AGE-02", "Age is too high"); }</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>= age</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>Test CheckedAge CheckedAgeTest</t>
         </is>
       </c>
-      <c r="C21" s="8" t="n"/>
-      <c r="D21" s="4" t="n"/>
-    </row>
-    <row r="22">
-      <c r="B22" s="9" t="inlineStr">
+      <c r="C23" s="8" t="n"/>
+      <c r="D23" s="4" t="n"/>
+    </row>
+    <row r="24">
+      <c r="B24" s="9" t="inlineStr">
         <is>
           <t>age</t>
         </is>
       </c>
-      <c r="C22" s="9" t="inlineStr">
+      <c r="C24" s="9" t="inlineStr">
         <is>
           <t>_res_</t>
         </is>
       </c>
-      <c r="D22" s="9" t="inlineStr">
+      <c r="D24" s="9" t="inlineStr">
         <is>
           <t>_error_</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="B23" s="5" t="inlineStr">
+    <row r="25">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>Age</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>Age</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>Error</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="B24" s="6" t="n">
+    <row r="26">
+      <c r="B26" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="C24" s="7" t="n">
+      <c r="C26" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="D24" s="7" t="n"/>
-    </row>
-    <row r="25">
-      <c r="B25" s="6" t="n">
+      <c r="D26" s="7" t="n"/>
+    </row>
+    <row r="27">
+      <c r="B27" s="6" t="n">
         <v>-1</v>
       </c>
-      <c r="C25" s="7" t="n"/>
-      <c r="D25" s="7" t="inlineStr">
+      <c r="C27" s="7" t="n"/>
+      <c r="D27" s="7" t="inlineStr">
         <is>
           <t>AGE-01: Age cannot be negative</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="B27" s="3" t="inlineStr">
+    <row r="29">
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>Test CheckedAge CheckedAgeCodeTest</t>
         </is>
       </c>
-      <c r="C27" s="8" t="n"/>
-      <c r="D27" s="8" t="n"/>
-      <c r="E27" s="4" t="n"/>
-    </row>
-    <row r="28">
-      <c r="B28" s="9" t="inlineStr">
+      <c r="C29" s="8" t="n"/>
+      <c r="D29" s="8" t="n"/>
+      <c r="E29" s="4" t="n"/>
+    </row>
+    <row r="30">
+      <c r="B30" s="9" t="inlineStr">
         <is>
           <t>age</t>
         </is>
       </c>
-      <c r="C28" s="9" t="inlineStr">
+      <c r="C30" s="9" t="inlineStr">
         <is>
           <t>_res_</t>
         </is>
       </c>
-      <c r="D28" s="9" t="inlineStr">
+      <c r="D30" s="9" t="inlineStr">
         <is>
           <t>_error_.code</t>
         </is>
       </c>
-      <c r="E28" s="9" t="inlineStr">
+      <c r="E30" s="9" t="inlineStr">
         <is>
           <t>_error_.message</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="B29" s="5" t="inlineStr">
+    <row r="31">
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>Age</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr">
+      <c r="C31" s="5" t="inlineStr">
         <is>
           <t>Age</t>
         </is>
       </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
       </c>
-      <c r="E29" s="5" t="inlineStr">
+      <c r="E31" s="5" t="inlineStr">
         <is>
           <t>Message</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="6" t="n">
-        <v>45</v>
-      </c>
-      <c r="C30" s="7" t="n">
-        <v>45</v>
-      </c>
-      <c r="D30" s="7" t="n"/>
-      <c r="E30" s="7" t="n"/>
-    </row>
-    <row r="31">
-      <c r="B31" s="6" t="n">
-        <v>-5</v>
-      </c>
-      <c r="C31" s="7" t="n"/>
-      <c r="D31" s="7" t="inlineStr">
-        <is>
-          <t>AGE-01</t>
-        </is>
-      </c>
-      <c r="E31" s="7" t="inlineStr">
-        <is>
-          <t>Age cannot be negative</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="C32" s="7" t="n">
+        <v>45</v>
+      </c>
+      <c r="D32" s="7" t="n"/>
+      <c r="E32" s="7" t="n"/>
+    </row>
+    <row r="33">
+      <c r="B33" s="6" t="n">
+        <v>-5</v>
+      </c>
+      <c r="C33" s="7" t="n"/>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>AGE-01</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>Age cannot be negative</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="6" t="n">
         <v>200</v>
       </c>
-      <c r="C32" s="7" t="n"/>
-      <c r="D32" s="7" t="inlineStr">
+      <c r="C34" s="7" t="n"/>
+      <c r="D34" s="7" t="inlineStr">
         <is>
           <t>AGE-02</t>
         </is>
       </c>
-      <c r="E32" s="7" t="inlineStr">
+      <c r="E34" s="7" t="inlineStr">
         <is>
           <t>Age is too high</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="16.5" customHeight="1">
-      <c r="B34" s="2" t="inlineStr">
+    <row r="36" ht="16.5" customHeight="1">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>"error(object)" raises an error with a body of any datatype. OpenL Rule Services returns the body as the response, and a test checks its fields with "_error_.&lt;field&gt;".</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="B36" s="3" t="inlineStr">
+    <row r="38">
+      <c r="B38" s="3" t="inlineStr">
         <is>
           <t>Datatype ValidationError</t>
         </is>
       </c>
-      <c r="C36" s="8" t="n"/>
-      <c r="D36" s="4" t="n"/>
-    </row>
-    <row r="37">
-      <c r="B37" s="6" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="C37" s="6" t="inlineStr">
-        <is>
-          <t>field</t>
-        </is>
-      </c>
-      <c r="D37" s="6" t="n"/>
-    </row>
-    <row r="38">
-      <c r="B38" s="6" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="C38" s="6" t="inlineStr">
-        <is>
-          <t>reason</t>
-        </is>
-      </c>
-      <c r="D38" s="6" t="n"/>
+      <c r="C38" s="8" t="n"/>
+      <c r="D38" s="4" t="n"/>
     </row>
     <row r="39">
       <c r="B39" s="6" t="inlineStr">
         <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>field</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="n"/>
+    </row>
+    <row r="40">
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>reason</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="n"/>
+    </row>
+    <row r="41">
+      <c r="B41" s="6" t="inlineStr">
+        <is>
           <t>Integer</t>
         </is>
       </c>
-      <c r="C39" s="6" t="inlineStr">
+      <c r="C41" s="6" t="inlineStr">
         <is>
           <t>severity</t>
         </is>
       </c>
-      <c r="D39" s="6" t="n">
+      <c r="D41" s="6" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="41">
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>Method String CheckedEmail(String email)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" s="6" t="inlineStr">
-        <is>
-          <t>if (!contains(email, "@")) { error(new ValidationError(field = "email", reason = "No @ sign")); }</t>
-        </is>
-      </c>
-    </row>
     <row r="43">
-      <c r="B43" s="6" t="inlineStr">
-        <is>
-          <t>return lowerCase(email);</t>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>Spreadsheet String CheckedEmail(String email)</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="n"/>
+    </row>
+    <row r="44">
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>Value</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="B45" s="3" t="inlineStr">
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>Check</t>
+        </is>
+      </c>
+      <c r="C45" s="12" t="inlineStr">
+        <is>
+          <t>= if (!contains(email, "@")) { error(new ValidationError(field = "email", reason = "No @ sign")); }</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+      <c r="C46" s="12" t="inlineStr">
+        <is>
+          <t>= lowerCase(email)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="3" t="inlineStr">
         <is>
           <t>Test CheckedEmail CheckedEmailTest</t>
         </is>
       </c>
-      <c r="C45" s="8" t="n"/>
-      <c r="D45" s="8" t="n"/>
-      <c r="E45" s="8" t="n"/>
-      <c r="F45" s="4" t="n"/>
-    </row>
-    <row r="46">
-      <c r="B46" s="9" t="inlineStr">
+      <c r="C48" s="8" t="n"/>
+      <c r="D48" s="8" t="n"/>
+      <c r="E48" s="8" t="n"/>
+      <c r="F48" s="4" t="n"/>
+    </row>
+    <row r="49">
+      <c r="B49" s="9" t="inlineStr">
         <is>
           <t>email</t>
         </is>
       </c>
-      <c r="C46" s="9" t="inlineStr">
+      <c r="C49" s="9" t="inlineStr">
         <is>
           <t>_res_</t>
         </is>
       </c>
-      <c r="D46" s="9" t="inlineStr">
+      <c r="D49" s="9" t="inlineStr">
         <is>
           <t>_error_.field</t>
         </is>
       </c>
-      <c r="E46" s="9" t="inlineStr">
+      <c r="E49" s="9" t="inlineStr">
         <is>
           <t>_error_.reason</t>
         </is>
       </c>
-      <c r="F46" s="9" t="inlineStr">
+      <c r="F49" s="9" t="inlineStr">
         <is>
           <t>_error_.severity</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="B47" s="5" t="inlineStr">
+    <row r="50">
+      <c r="B50" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="C47" s="5" t="inlineStr">
+      <c r="C50" s="5" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-      <c r="D47" s="5" t="inlineStr">
+      <c r="D50" s="5" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="E47" s="5" t="inlineStr">
+      <c r="E50" s="5" t="inlineStr">
         <is>
           <t>Reason</t>
         </is>
       </c>
-      <c r="F47" s="5" t="inlineStr">
+      <c r="F50" s="5" t="inlineStr">
         <is>
           <t>Severity</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="B48" s="6" t="inlineStr">
+    <row r="51">
+      <c r="B51" s="6" t="inlineStr">
         <is>
           <t>Ann@Example.com</t>
         </is>
       </c>
-      <c r="C48" s="7" t="inlineStr">
+      <c r="C51" s="7" t="inlineStr">
         <is>
           <t>ann@example.com</t>
         </is>
       </c>
-      <c r="D48" s="7" t="n"/>
-      <c r="E48" s="7" t="n"/>
-      <c r="F48" s="7" t="n"/>
-    </row>
-    <row r="49">
-      <c r="B49" s="6" t="inlineStr">
+      <c r="D51" s="7" t="n"/>
+      <c r="E51" s="7" t="n"/>
+      <c r="F51" s="7" t="n"/>
+    </row>
+    <row r="52">
+      <c r="B52" s="6" t="inlineStr">
         <is>
           <t>wrong.example.com</t>
         </is>
       </c>
-      <c r="C49" s="7" t="n"/>
-      <c r="D49" s="7" t="inlineStr">
+      <c r="C52" s="7" t="n"/>
+      <c r="D52" s="7" t="inlineStr">
         <is>
           <t>email</t>
         </is>
       </c>
-      <c r="E49" s="7" t="inlineStr">
+      <c r="E52" s="7" t="inlineStr">
         <is>
           <t>No @ sign</t>
         </is>
       </c>
-      <c r="F49" s="7" t="n">
+      <c r="F52" s="7" t="n">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="B27:E27"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="B34:I34"/>
-    <mergeCell ref="B45:F45"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="B10:E10"/>
+  <mergeCells count="10">
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B48:F48"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B29:E29"/>
+    <mergeCell ref="B11:E11"/>
+    <mergeCell ref="B36:I36"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B38:D38"/>
     <mergeCell ref="B4:I4"/>
+    <mergeCell ref="B43:C43"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
